--- a/data/trans_camb/P16A15-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A15-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 7,14</t>
+          <t>-0,09; 7,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 6,32</t>
+          <t>-0,81; 6,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,93; 9,33</t>
+          <t>2,83; 9,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 4,89</t>
+          <t>-2,39; 4,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 3,23</t>
+          <t>-3,95; 3,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 9,26</t>
+          <t>2,38; 8,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 5,17</t>
+          <t>-0,2; 4,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 3,82</t>
+          <t>-1,03; 3,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,57; 8,29</t>
+          <t>3,48; 8,19</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 165,99</t>
+          <t>-1,17; 176,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 154,68</t>
+          <t>-12,42; 146,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35,02; 215,26</t>
+          <t>36,12; 241,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-44,73; 159,22</t>
+          <t>-40,73; 169,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-60,99; 112,5</t>
+          <t>-61,74; 118,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,63; 343,06</t>
+          <t>34,86; 349,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 131,08</t>
+          <t>-4,07; 116,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-19,42; 92,88</t>
+          <t>-18,15; 89,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>55,5; 202,0</t>
+          <t>49,34; 196,26</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 7,72</t>
+          <t>-0,24; 7,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 6,63</t>
+          <t>-0,67; 6,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,62; 12,48</t>
+          <t>4,62; 12,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 7,2</t>
+          <t>0,47; 6,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 6,19</t>
+          <t>0,28; 6,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,44; 8,96</t>
+          <t>3,19; 9,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 6,36</t>
+          <t>1,31; 6,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 5,51</t>
+          <t>0,78; 5,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,13; 9,81</t>
+          <t>5,27; 10,03</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 221,0</t>
+          <t>-3,71; 183,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 181,92</t>
+          <t>-11,9; 166,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58,25; 366,41</t>
+          <t>59,66; 327,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 374,85</t>
+          <t>7,78; 366,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 328,36</t>
+          <t>-1,78; 326,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,31; 484,39</t>
+          <t>65,79; 524,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,34; 195,25</t>
+          <t>24,41; 201,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,33; 164,38</t>
+          <t>13,7; 182,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>93,72; 308,06</t>
+          <t>92,87; 320,6</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,89; 9,5</t>
+          <t>3,1; 9,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,44; 9,29</t>
+          <t>2,39; 9,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 10,68</t>
+          <t>-2,46; 10,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 6,21</t>
+          <t>-3,89; 5,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 13,93</t>
+          <t>-0,25; 12,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,05; 14,91</t>
+          <t>4,41; 15,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,07; 7,79</t>
+          <t>2,05; 7,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,11; 9,12</t>
+          <t>2,7; 8,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 10,58</t>
+          <t>-1,66; 10,29</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37,79; 230,31</t>
+          <t>40,62; 211,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30,36; 218,27</t>
+          <t>35,6; 226,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-34,23; 209,12</t>
+          <t>-36,69; 210,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-37,85; 173,83</t>
+          <t>-44,43; 141,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 344,12</t>
+          <t>-7,98; 321,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33,94; 387,32</t>
+          <t>39,64; 407,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,4; 172,2</t>
+          <t>26,81; 168,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>41,71; 200,45</t>
+          <t>36,67; 193,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-35,97; 197,97</t>
+          <t>-26,22; 186,9</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,15; 7,11</t>
+          <t>2,02; 6,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 5,16</t>
+          <t>0,58; 4,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,92; 8,83</t>
+          <t>3,84; 8,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 4,98</t>
+          <t>-0,51; 5,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 3,34</t>
+          <t>-1,43; 3,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,32; 56,16</t>
+          <t>4,22; 59,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,43</t>
+          <t>1,82; 5,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 3,48</t>
+          <t>0,21; 3,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,26; 39,9</t>
+          <t>5,11; 41,4</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>24,48; 108,24</t>
+          <t>23,09; 106,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,72; 77,66</t>
+          <t>6,75; 74,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43,75; 133,56</t>
+          <t>43,66; 132,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 105,38</t>
+          <t>-8,56; 110,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,21; 73,03</t>
+          <t>-20,38; 75,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>69,17; 1869,53</t>
+          <t>67,37; 1502,95</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,7; 87,43</t>
+          <t>24,43; 89,78</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,32; 56,96</t>
+          <t>3,44; 66,96</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>72,3; 611,08</t>
+          <t>70,81; 635,18</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,33; 10,56</t>
+          <t>3,56; 10,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,21; 9,78</t>
+          <t>3,42; 9,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,01; 10,65</t>
+          <t>4,01; 10,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,79; 10,93</t>
+          <t>3,72; 10,67</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,08; 9,32</t>
+          <t>2,24; 8,94</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,13; 12,75</t>
+          <t>4,9; 13,37</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,69; 9,9</t>
+          <t>4,64; 9,66</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,47; 8,4</t>
+          <t>3,32; 8,11</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,53; 11,43</t>
+          <t>5,68; 11,41</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>45,83; 325,47</t>
+          <t>52,92; 319,0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>48,02; 306,57</t>
+          <t>48,03; 305,09</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>59,39; 335,07</t>
+          <t>55,38; 359,9</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>40,49; 177,88</t>
+          <t>37,0; 164,11</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>19,32; 147,13</t>
+          <t>22,8; 144,69</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,06; 196,38</t>
+          <t>53,81; 211,98</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>57,18; 182,04</t>
+          <t>57,97; 174,04</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>41,81; 155,69</t>
+          <t>40,51; 143,24</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>71,89; 216,64</t>
+          <t>74,57; 212,37</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 2,72</t>
+          <t>-1,35; 3,21</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 1,63</t>
+          <t>-1,63; 1,47</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 2,11</t>
+          <t>-1,21; 2,34</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,37; 9,19</t>
+          <t>3,42; 9,38</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,61; 7,5</t>
+          <t>1,41; 7,69</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,63; 8,16</t>
+          <t>2,81; 8,12</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,56; 7,52</t>
+          <t>2,66; 7,62</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,78; 6,0</t>
+          <t>0,85; 5,77</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,51; 5,95</t>
+          <t>1,58; 5,96</t>
         </is>
       </c>
     </row>
@@ -1873,37 +1873,37 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-77,75; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26,81; 90,31</t>
+          <t>26,56; 93,12</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>12,14; 70,16</t>
+          <t>10,43; 74,5</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18,97; 78,54</t>
+          <t>21,73; 79,77</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>23,09; 86,11</t>
+          <t>24,69; 88,96</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6,28; 69,9</t>
+          <t>7,25; 66,34</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>14,1; 71,26</t>
+          <t>14,84; 71,4</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,96; 5,84</t>
+          <t>3,26; 5,88</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,4; 4,84</t>
+          <t>2,23; 4,94</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3,16; 7,36</t>
+          <t>2,98; 7,28</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,92; 5,96</t>
+          <t>2,99; 5,87</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,54</t>
+          <t>1,63; 4,54</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,57; 26,14</t>
+          <t>5,53; 26,6</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,4; 5,44</t>
+          <t>3,3; 5,41</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,4</t>
+          <t>2,4; 4,36</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5,46; 16,05</t>
+          <t>5,31; 17,4</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>46,62; 110,18</t>
+          <t>50,69; 112,49</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>36,6; 92,66</t>
+          <t>35,04; 96,18</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>55,82; 137,02</t>
+          <t>49,61; 141,05</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>33,69; 81,08</t>
+          <t>35,58; 81,16</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>19,3; 62,2</t>
+          <t>18,67; 61,76</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>69,3; 352,7</t>
+          <t>68,08; 343,53</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>46,16; 84,13</t>
+          <t>45,0; 84,43</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>31,92; 68,45</t>
+          <t>33,28; 68,67</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>77,68; 242,67</t>
+          <t>75,92; 257,43</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A15-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A15-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,11</t>
+          <t>6,1</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,94</t>
+          <t>5,91</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,94</t>
+          <t>5,92</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 7,42</t>
+          <t>-0,16; 7,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 6,24</t>
+          <t>-0,61; 6,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 9,76</t>
+          <t>3,02; 9,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 4,89</t>
+          <t>-2,64; 4,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 3,18</t>
+          <t>-3,48; 3,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 8,99</t>
+          <t>2,45; 9,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 4,93</t>
+          <t>-0,21; 5,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 3,8</t>
+          <t>-0,93; 3,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,48; 8,19</t>
+          <t>3,6; 8,08</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>106,99%</t>
+          <t>106,67%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>130,16%</t>
+          <t>129,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>112,94%</t>
+          <t>112,49%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 176,91</t>
+          <t>-5,45; 165,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 146,28</t>
+          <t>-10,36; 154,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36,12; 241,65</t>
+          <t>39,92; 229,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-40,73; 169,5</t>
+          <t>-46,3; 156,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,74; 118,21</t>
+          <t>-57,12; 111,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,86; 349,37</t>
+          <t>34,07; 364,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 116,21</t>
+          <t>-4,23; 119,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 89,36</t>
+          <t>-15,15; 97,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>49,34; 196,26</t>
+          <t>53,26; 202,44</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,44</t>
+          <t>8,46</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,29</t>
+          <t>6,14</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7,56</t>
+          <t>7,46</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 7,14</t>
+          <t>0,36; 7,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 6,39</t>
+          <t>-0,88; 6,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,62; 12,29</t>
+          <t>4,53; 11,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 6,94</t>
+          <t>0,44; 7,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 6,59</t>
+          <t>0,32; 6,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,19; 9,2</t>
+          <t>3,5; 9,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 6,45</t>
+          <t>1,35; 6,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 5,7</t>
+          <t>0,56; 5,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,27; 10,03</t>
+          <t>5,16; 10,0</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>156,02%</t>
+          <t>156,23%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>209,22%</t>
+          <t>204,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>180,07%</t>
+          <t>177,7%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 183,27</t>
+          <t>1,71; 215,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 166,68</t>
+          <t>-13,1; 177,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59,66; 327,69</t>
+          <t>58,67; 324,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,78; 366,0</t>
+          <t>-0,9; 397,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 326,47</t>
+          <t>-1,29; 354,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,79; 524,58</t>
+          <t>64,87; 480,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,41; 201,41</t>
+          <t>22,69; 197,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,7; 182,35</t>
+          <t>9,82; 158,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>92,87; 320,6</t>
+          <t>99,7; 326,68</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,96</t>
+          <t>8,85</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,0</t>
+          <t>9,54</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,13</t>
+          <t>9,1</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,1; 9,52</t>
+          <t>2,73; 9,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 9,28</t>
+          <t>2,32; 9,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 10,95</t>
+          <t>5,64; 12,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 5,84</t>
+          <t>-4,76; 6,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 12,6</t>
+          <t>-1,01; 12,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,41; 15,52</t>
+          <t>3,74; 14,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,05; 7,74</t>
+          <t>2,07; 7,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,7; 8,85</t>
+          <t>2,89; 8,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 10,29</t>
+          <t>6,12; 11,93</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>158,37%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>152,55%</t>
+          <t>145,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>156,36%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>40,62; 211,28</t>
+          <t>37,56; 221,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35,6; 226,29</t>
+          <t>31,67; 233,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-36,69; 210,74</t>
+          <t>73,4; 297,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-44,43; 141,62</t>
+          <t>-48,58; 154,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 321,82</t>
+          <t>-15,22; 316,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>39,64; 407,97</t>
+          <t>29,9; 388,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,81; 168,06</t>
+          <t>28,0; 162,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>36,67; 193,44</t>
+          <t>38,57; 189,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-26,22; 186,9</t>
+          <t>83,55; 251,62</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,45</t>
+          <t>6,07</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,63</t>
+          <t>4,85</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>14,59</t>
+          <t>5,43</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,02; 6,95</t>
+          <t>1,96; 7,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 4,92</t>
+          <t>0,64; 5,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,84; 8,64</t>
+          <t>3,62; 8,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 5,12</t>
+          <t>-0,41; 4,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 3,33</t>
+          <t>-1,53; 3,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,22; 59,32</t>
+          <t>2,39; 7,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,48</t>
+          <t>1,67; 5,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 3,73</t>
+          <t>0,21; 3,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,11; 41,4</t>
+          <t>3,74; 7,36</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>406,45%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>211,22%</t>
+          <t>78,62%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>23,09; 106,59</t>
+          <t>23,3; 107,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,75; 74,5</t>
+          <t>7,31; 81,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43,66; 132,53</t>
+          <t>42,41; 128,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 110,63</t>
+          <t>-7,27; 106,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-20,38; 75,2</t>
+          <t>-22,39; 71,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>67,37; 1502,95</t>
+          <t>31,61; 161,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,43; 89,78</t>
+          <t>21,54; 88,59</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,44; 66,96</t>
+          <t>2,88; 56,93</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>70,81; 635,18</t>
+          <t>47,68; 119,79</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7,47</t>
+          <t>6,1</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,51</t>
+          <t>11,32</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8,84</t>
+          <t>9,12</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,56; 10,43</t>
+          <t>3,57; 10,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,42; 9,71</t>
+          <t>3,43; 9,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,01; 10,94</t>
+          <t>3,06; 9,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,72; 10,67</t>
+          <t>3,92; 10,93</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,24; 8,94</t>
+          <t>2,08; 9,34</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,9; 13,37</t>
+          <t>8,32; 14,59</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,64; 9,66</t>
+          <t>4,5; 9,47</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,32; 8,11</t>
+          <t>2,97; 8,0</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,68; 11,41</t>
+          <t>7,03; 11,34</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>160,61%</t>
+          <t>131,09%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>121,3%</t>
+          <t>144,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>133,35%</t>
+          <t>137,6%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>52,92; 319,0</t>
+          <t>56,79; 322,8</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>48,03; 305,09</t>
+          <t>50,32; 309,85</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>55,38; 359,9</t>
+          <t>43,78; 295,63</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>37,0; 164,11</t>
+          <t>41,59; 191,09</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>22,8; 144,69</t>
+          <t>21,03; 148,11</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,81; 211,98</t>
+          <t>82,48; 235,66</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>57,97; 174,04</t>
+          <t>57,72; 171,78</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>40,51; 143,24</t>
+          <t>33,83; 139,15</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>74,57; 212,37</t>
+          <t>85,38; 208,95</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,44</t>
+          <t>5,2</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3,76</t>
+          <t>3,89</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 3,21</t>
+          <t>-1,39; 2,62</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 1,47</t>
+          <t>-1,69; 1,57</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,34</t>
+          <t>-1,11; 2,36</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,42; 9,38</t>
+          <t>3,42; 9,53</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,41; 7,69</t>
+          <t>1,69; 7,59</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,81; 8,12</t>
+          <t>2,29; 7,91</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,66; 7,62</t>
+          <t>2,51; 7,53</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,77</t>
+          <t>1,01; 5,85</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,96</t>
+          <t>1,7; 6,22</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>40,87%</t>
         </is>
       </c>
     </row>
@@ -1873,37 +1873,37 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-77,75; —</t>
+          <t>-77,1; 890,12</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26,56; 93,12</t>
+          <t>25,69; 90,96</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>10,43; 74,5</t>
+          <t>12,97; 72,34</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>21,73; 79,77</t>
+          <t>17,41; 76,54</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>24,69; 88,96</t>
+          <t>23,72; 88,98</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>7,25; 66,34</t>
+          <t>8,75; 69,34</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>14,84; 71,4</t>
+          <t>15,87; 75,91</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5,81</t>
+          <t>6,36</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,93</t>
+          <t>6,2</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>8,46</t>
+          <t>6,29</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>3,26; 5,88</t>
+          <t>3,17; 5,79</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,23; 4,94</t>
+          <t>2,35; 4,83</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2,98; 7,28</t>
+          <t>5,12; 7,64</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,99; 5,87</t>
+          <t>3,0; 6,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,54</t>
+          <t>1,61; 4,57</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,53; 26,6</t>
+          <t>4,93; 7,54</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,3; 5,41</t>
+          <t>3,49; 5,38</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2,4; 4,36</t>
+          <t>2,36; 4,34</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5,31; 17,4</t>
+          <t>5,5; 7,26</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>100,14%</t>
+          <t>109,64%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>138,41%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>123,15%</t>
+          <t>91,62%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>50,69; 112,49</t>
+          <t>50,36; 112,2</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>35,04; 96,18</t>
+          <t>37,09; 94,93</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>49,61; 141,05</t>
+          <t>80,66; 146,4</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>35,58; 81,16</t>
+          <t>34,59; 83,65</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>18,67; 61,76</t>
+          <t>18,45; 63,26</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>68,08; 343,53</t>
+          <t>56,38; 104,87</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>45,0; 84,43</t>
+          <t>47,35; 83,64</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>33,28; 68,67</t>
+          <t>31,57; 67,46</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>75,92; 257,43</t>
+          <t>75,5; 113,05</t>
         </is>
       </c>
     </row>
